--- a/pr.xlsx
+++ b/pr.xlsx
@@ -27521,7 +27521,7 @@
       </c>
       <c r="S396" t="inlineStr">
         <is>
-          <t>ACTIVE_LINES_PRICED</t>
+          <t>NO_CURRENT_WORK_ITEM</t>
         </is>
       </c>
     </row>
@@ -42132,7 +42132,7 @@
       </c>
       <c r="S570" t="inlineStr">
         <is>
-          <t>ACTIVE_LINES_PRICED</t>
+          <t>NO_CURRENT_WORK_ITEM</t>
         </is>
       </c>
     </row>
@@ -68124,7 +68124,7 @@
       </c>
       <c r="S947" t="inlineStr">
         <is>
-          <t>NO_CURRENT_WORK_ITEM</t>
+          <t>ACTIVE_LINES_NOT_FULLY_PRICED</t>
         </is>
       </c>
     </row>
@@ -68257,7 +68257,7 @@
       </c>
       <c r="S949" t="inlineStr">
         <is>
-          <t>ACTIVE_LINES_PRICED</t>
+          <t>NO_CURRENT_WORK_ITEM</t>
         </is>
       </c>
     </row>
@@ -69188,7 +69188,7 @@
       </c>
       <c r="S962" t="inlineStr">
         <is>
-          <t>UNMAPPED_ELEMENT</t>
+          <t>ACTIVE_LINES_PRICED</t>
         </is>
       </c>
     </row>
@@ -69824,7 +69824,7 @@
       </c>
       <c r="S971" t="inlineStr">
         <is>
-          <t>NO_CURRENT_WORK_ITEM</t>
+          <t>ACTIVE_LINES_NOT_FULLY_PRICED</t>
         </is>
       </c>
     </row>
